--- a/public/resources/MikeYe-Post-Deal-Integration-Checklist-v1.0.xlsx
+++ b/public/resources/MikeYe-Post-Deal-Integration-Checklist-v1.0.xlsx
@@ -2,13 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R929984b848cc4442"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integration Plan" sheetId="2" r:id="Rcbc958c419bb4c5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 1 Readiness" sheetId="3" r:id="R82d78a2a409246ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workflow Decisions" sheetId="4" r:id="R5c968b8534cb4830"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synergies" sheetId="5" r:id="R5b064f6f73ea471b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks &amp; Decisions" sheetId="6" r:id="Rddd4a0c80e1e4f63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="7" r:id="R199ab01113d34f7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Reb7938defcdf456a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integration Plan" sheetId="2" r:id="Rd0e4c127b40e41a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 1 Readiness" sheetId="3" r:id="R0b71a6a4ca484555"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workflow Decisions" sheetId="4" r:id="R0c4b677eea7f4519"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synergies" sheetId="5" r:id="R308b3ef3b4814c46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks &amp; Decisions" sheetId="6" r:id="Rdbe42b34c95c422a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -22,7 +21,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="$#,##0"/>
   </x:numFmts>
-  <x:fonts count="8">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -60,11 +59,6 @@
       <x:b/>
       <x:sz val="14"/>
       <x:color rgb="FF1A1A18"/>
-      <x:name val="Arial"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:color rgb="FF1D4E89"/>
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
@@ -143,7 +137,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="57">
+  <x:cellXfs count="55">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -281,12 +275,6 @@
     <x:xf numFmtId="200" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -341,9 +329,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="IntegrationPlanTable" displayName="IntegrationPlanTable" ref="A5:S109" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:S109"/>
-  <x:tableColumns count="19">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="IntegrationPlanTable" displayName="IntegrationPlanTable" ref="A5:R109" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:R109"/>
+  <x:tableColumns count="18">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Phase"/>
     <x:tableColumn id="3" name="Workstream"/>
@@ -362,7 +350,6 @@
     <x:tableColumn id="16" name="Decision / escalation"/>
     <x:tableColumn id="17" name="Notes"/>
     <x:tableColumn id="18" name="Reviewer decision"/>
-    <x:tableColumn id="19" name="Source IDs"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -454,21 +441,6 @@
     <x:tableColumn id="11" name="Resolution"/>
     <x:tableColumn id="12" name="Status"/>
     <x:tableColumn id="13" name="Reviewer decision"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="IntegrationSourcesTable" displayName="IntegrationSourcesTable" ref="A5:F11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:F11"/>
-  <x:tableColumns count="6">
-    <x:tableColumn id="1" name="Source ID"/>
-    <x:tableColumn id="2" name="Organization"/>
-    <x:tableColumn id="3" name="Resource"/>
-    <x:tableColumn id="4" name="Accessed"/>
-    <x:tableColumn id="5" name="URL"/>
-    <x:tableColumn id="6" name="Use in this workbook"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -944,7 +916,6 @@
     <x:col min="16" max="16" width="32" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="30" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" ht="24" customHeight="1">
@@ -976,7 +947,6 @@
       <x:c r="P4" s="5"/>
       <x:c r="Q4" s="5"/>
       <x:c r="R4" s="5"/>
-      <x:c r="S4" s="5"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="50" t="str">
@@ -1032,9 +1002,6 @@
       </x:c>
       <x:c r="R5" s="50" t="str">
         <x:v>Reviewer decision</x:v>
-      </x:c>
-      <x:c r="S5" s="50" t="str">
-        <x:v>Source IDs</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
@@ -1080,9 +1047,6 @@
       <x:c r="R6" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S6" s="51" t="str">
-        <x:v>S10;M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="7" ht="42" customHeight="1">
       <x:c r="A7" s="51" t="str">
@@ -1127,9 +1091,6 @@
       <x:c r="R7" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S7" s="51" t="str">
-        <x:v>S10;M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="8" ht="42" customHeight="1">
       <x:c r="A8" s="51" t="str">
@@ -1174,9 +1135,6 @@
       <x:c r="R8" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S8" s="51" t="str">
-        <x:v>S12</x:v>
-      </x:c>
     </x:row>
     <x:row r="9" ht="42" customHeight="1">
       <x:c r="A9" s="51" t="str">
@@ -1221,9 +1179,6 @@
       <x:c r="R9" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S9" s="51" t="str">
-        <x:v>S12;M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="10" ht="42" customHeight="1">
       <x:c r="A10" s="51" t="str">
@@ -1268,9 +1223,6 @@
       <x:c r="R10" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S10" s="51" t="str">
-        <x:v>S12</x:v>
-      </x:c>
     </x:row>
     <x:row r="11" ht="42" customHeight="1">
       <x:c r="A11" s="51" t="str">
@@ -1315,9 +1267,6 @@
       <x:c r="R11" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S11" s="51" t="str">
-        <x:v>S11</x:v>
-      </x:c>
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
       <x:c r="A12" s="51" t="str">
@@ -1362,9 +1311,6 @@
       <x:c r="R12" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S12" s="51" t="str">
-        <x:v>S10;S12</x:v>
-      </x:c>
     </x:row>
     <x:row r="13" ht="42" customHeight="1">
       <x:c r="A13" s="51" t="str">
@@ -1409,9 +1355,6 @@
       <x:c r="R13" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S13" s="51" t="str">
-        <x:v>S12;S13</x:v>
-      </x:c>
     </x:row>
     <x:row r="14" ht="42" customHeight="1">
       <x:c r="A14" s="51" t="str">
@@ -1456,9 +1399,6 @@
       <x:c r="R14" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S14" s="51" t="str">
-        <x:v>S05</x:v>
-      </x:c>
     </x:row>
     <x:row r="15" ht="42" customHeight="1">
       <x:c r="A15" s="51" t="str">
@@ -1503,9 +1443,6 @@
       <x:c r="R15" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S15" s="51" t="str">
-        <x:v>S05</x:v>
-      </x:c>
     </x:row>
     <x:row r="16" ht="42" customHeight="1">
       <x:c r="A16" s="51" t="str">
@@ -1550,9 +1487,6 @@
       <x:c r="R16" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S16" s="51" t="str">
-        <x:v>S05</x:v>
-      </x:c>
     </x:row>
     <x:row r="17" ht="42" customHeight="1">
       <x:c r="A17" s="51" t="str">
@@ -1597,9 +1531,6 @@
       <x:c r="R17" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S17" s="51" t="str">
-        <x:v>S05</x:v>
-      </x:c>
     </x:row>
     <x:row r="18" ht="42" customHeight="1">
       <x:c r="A18" s="51" t="str">
@@ -1644,9 +1575,6 @@
       <x:c r="R18" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S18" s="51" t="str">
-        <x:v>S11;M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="19" ht="42" customHeight="1">
       <x:c r="A19" s="51" t="str">
@@ -1691,9 +1619,6 @@
       <x:c r="R19" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S19" s="51" t="str">
-        <x:v>S11;S12</x:v>
-      </x:c>
     </x:row>
     <x:row r="20" ht="42" customHeight="1">
       <x:c r="A20" s="51" t="str">
@@ -1738,9 +1663,6 @@
       <x:c r="R20" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S20" s="51" t="str">
-        <x:v>S11;M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="21" ht="42" customHeight="1">
       <x:c r="A21" s="51" t="str">
@@ -1785,9 +1707,6 @@
       <x:c r="R21" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S21" s="51" t="str">
-        <x:v>S11</x:v>
-      </x:c>
     </x:row>
     <x:row r="22" ht="42" customHeight="1">
       <x:c r="A22" s="51" t="str">
@@ -1832,9 +1751,6 @@
       <x:c r="R22" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S22" s="51" t="str">
-        <x:v>S11;S12</x:v>
-      </x:c>
     </x:row>
     <x:row r="23" ht="42" customHeight="1">
       <x:c r="A23" s="51" t="str">
@@ -1879,9 +1795,6 @@
       <x:c r="R23" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S23" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="24" ht="42" customHeight="1">
       <x:c r="A24" s="51" t="str">
@@ -1926,9 +1839,6 @@
       <x:c r="R24" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S24" s="51" t="str">
-        <x:v>S11;S12</x:v>
-      </x:c>
     </x:row>
     <x:row r="25" ht="42" customHeight="1">
       <x:c r="A25" s="51" t="str">
@@ -1973,9 +1883,6 @@
       <x:c r="R25" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S25" s="51" t="str">
-        <x:v>S12</x:v>
-      </x:c>
     </x:row>
     <x:row r="26" ht="42" customHeight="1">
       <x:c r="A26" s="51" t="str">
@@ -2020,9 +1927,6 @@
       <x:c r="R26" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S26" s="51" t="str">
-        <x:v>S11</x:v>
-      </x:c>
     </x:row>
     <x:row r="27" ht="42" customHeight="1">
       <x:c r="A27" s="51" t="str">
@@ -2067,9 +1971,6 @@
       <x:c r="R27" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S27" s="51" t="str">
-        <x:v>S12</x:v>
-      </x:c>
     </x:row>
     <x:row r="28" ht="42" customHeight="1">
       <x:c r="A28" s="51" t="str">
@@ -2114,9 +2015,6 @@
       <x:c r="R28" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S28" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="29" ht="42" customHeight="1">
       <x:c r="A29" s="51" t="str">
@@ -2161,9 +2059,6 @@
       <x:c r="R29" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S29" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="30" ht="42" customHeight="1">
       <x:c r="A30" s="51" t="str">
@@ -2208,9 +2103,6 @@
       <x:c r="R30" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S30" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="31" ht="42" customHeight="1">
       <x:c r="A31" s="51" t="str">
@@ -2255,9 +2147,6 @@
       <x:c r="R31" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S31" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="32" ht="42" customHeight="1">
       <x:c r="A32" s="51" t="str">
@@ -2302,9 +2191,6 @@
       <x:c r="R32" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S32" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="33" ht="42" customHeight="1">
       <x:c r="A33" s="51" t="str">
@@ -2349,9 +2235,6 @@
       <x:c r="R33" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S33" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="34" ht="42" customHeight="1">
       <x:c r="A34" s="51" t="str">
@@ -2396,9 +2279,6 @@
       <x:c r="R34" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S34" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="35" ht="42" customHeight="1">
       <x:c r="A35" s="51" t="str">
@@ -2443,9 +2323,6 @@
       <x:c r="R35" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S35" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="36" ht="42" customHeight="1">
       <x:c r="A36" s="51" t="str">
@@ -2490,9 +2367,6 @@
       <x:c r="R36" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S36" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="37" ht="42" customHeight="1">
       <x:c r="A37" s="51" t="str">
@@ -2537,9 +2411,6 @@
       <x:c r="R37" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S37" s="51" t="str">
-        <x:v>S11</x:v>
-      </x:c>
     </x:row>
     <x:row r="38" ht="42" customHeight="1">
       <x:c r="A38" s="51" t="str">
@@ -2584,9 +2455,6 @@
       <x:c r="R38" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S38" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="39" ht="42" customHeight="1">
       <x:c r="A39" s="51" t="str">
@@ -2631,9 +2499,6 @@
       <x:c r="R39" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S39" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="40" ht="42" customHeight="1">
       <x:c r="A40" s="51" t="str">
@@ -2678,9 +2543,6 @@
       <x:c r="R40" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S40" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="41" ht="42" customHeight="1">
       <x:c r="A41" s="51" t="str">
@@ -2725,9 +2587,6 @@
       <x:c r="R41" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S41" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="42" ht="42" customHeight="1">
       <x:c r="A42" s="51" t="str">
@@ -2772,9 +2631,6 @@
       <x:c r="R42" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S42" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="43" ht="42" customHeight="1">
       <x:c r="A43" s="51" t="str">
@@ -2819,9 +2675,6 @@
       <x:c r="R43" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S43" s="51" t="str">
-        <x:v>S11</x:v>
-      </x:c>
     </x:row>
     <x:row r="44" ht="42" customHeight="1">
       <x:c r="A44" s="51" t="str">
@@ -2866,9 +2719,6 @@
       <x:c r="R44" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S44" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="45" ht="42" customHeight="1">
       <x:c r="A45" s="51" t="str">
@@ -2913,9 +2763,6 @@
       <x:c r="R45" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S45" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="46" ht="42" customHeight="1">
       <x:c r="A46" s="51" t="str">
@@ -2960,9 +2807,6 @@
       <x:c r="R46" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S46" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="47" ht="42" customHeight="1">
       <x:c r="A47" s="51" t="str">
@@ -3007,9 +2851,6 @@
       <x:c r="R47" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S47" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="48" ht="42" customHeight="1">
       <x:c r="A48" s="51" t="str">
@@ -3054,9 +2895,6 @@
       <x:c r="R48" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S48" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="49" ht="42" customHeight="1">
       <x:c r="A49" s="51" t="str">
@@ -3101,9 +2939,6 @@
       <x:c r="R49" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S49" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="50" ht="42" customHeight="1">
       <x:c r="A50" s="51" t="str">
@@ -3148,9 +2983,6 @@
       <x:c r="R50" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S50" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="51" ht="42" customHeight="1">
       <x:c r="A51" s="51" t="str">
@@ -3195,9 +3027,6 @@
       <x:c r="R51" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S51" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="52" ht="42" customHeight="1">
       <x:c r="A52" s="51" t="str">
@@ -3242,9 +3071,6 @@
       <x:c r="R52" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S52" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="53" ht="42" customHeight="1">
       <x:c r="A53" s="51" t="str">
@@ -3289,9 +3115,6 @@
       <x:c r="R53" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S53" s="51" t="str">
-        <x:v>S13;M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="54" ht="42" customHeight="1">
       <x:c r="A54" s="51" t="str">
@@ -3336,9 +3159,6 @@
       <x:c r="R54" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S54" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="55" ht="42" customHeight="1">
       <x:c r="A55" s="51" t="str">
@@ -3383,9 +3203,6 @@
       <x:c r="R55" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S55" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="56" ht="42" customHeight="1">
       <x:c r="A56" s="51" t="str">
@@ -3430,9 +3247,6 @@
       <x:c r="R56" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S56" s="51" t="str">
-        <x:v>S12;M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="57" ht="42" customHeight="1">
       <x:c r="A57" s="51" t="str">
@@ -3477,9 +3291,6 @@
       <x:c r="R57" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S57" s="51" t="str">
-        <x:v>S11</x:v>
-      </x:c>
     </x:row>
     <x:row r="58" ht="42" customHeight="1">
       <x:c r="A58" s="51" t="str">
@@ -3524,9 +3335,6 @@
       <x:c r="R58" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S58" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="59" ht="42" customHeight="1">
       <x:c r="A59" s="51" t="str">
@@ -3571,9 +3379,6 @@
       <x:c r="R59" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S59" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="60" ht="42" customHeight="1">
       <x:c r="A60" s="51" t="str">
@@ -3618,9 +3423,6 @@
       <x:c r="R60" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S60" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="61" ht="42" customHeight="1">
       <x:c r="A61" s="51" t="str">
@@ -3665,9 +3467,6 @@
       <x:c r="R61" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S61" s="51" t="str">
-        <x:v>S11;M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="62" ht="42" customHeight="1">
       <x:c r="A62" s="51" t="str">
@@ -3712,9 +3511,6 @@
       <x:c r="R62" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S62" s="51" t="str">
-        <x:v>S11</x:v>
-      </x:c>
     </x:row>
     <x:row r="63" ht="42" customHeight="1">
       <x:c r="A63" s="51" t="str">
@@ -3759,9 +3555,6 @@
       <x:c r="R63" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S63" s="51" t="str">
-        <x:v>S11</x:v>
-      </x:c>
     </x:row>
     <x:row r="64" ht="42" customHeight="1">
       <x:c r="A64" s="51" t="str">
@@ -3806,9 +3599,6 @@
       <x:c r="R64" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S64" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="65" ht="42" customHeight="1">
       <x:c r="A65" s="51" t="str">
@@ -3853,9 +3643,6 @@
       <x:c r="R65" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S65" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="66" ht="42" customHeight="1">
       <x:c r="A66" s="51" t="str">
@@ -3900,9 +3687,6 @@
       <x:c r="R66" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S66" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="67" ht="42" customHeight="1">
       <x:c r="A67" s="51" t="str">
@@ -3947,9 +3731,6 @@
       <x:c r="R67" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S67" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="68" ht="42" customHeight="1">
       <x:c r="A68" s="51" t="str">
@@ -3994,9 +3775,6 @@
       <x:c r="R68" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S68" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="69" ht="42" customHeight="1">
       <x:c r="A69" s="51" t="str">
@@ -4041,9 +3819,6 @@
       <x:c r="R69" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S69" s="51" t="str">
-        <x:v>S11</x:v>
-      </x:c>
     </x:row>
     <x:row r="70" ht="42" customHeight="1">
       <x:c r="A70" s="51" t="str">
@@ -4088,9 +3863,6 @@
       <x:c r="R70" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S70" s="51" t="str">
-        <x:v>S11</x:v>
-      </x:c>
     </x:row>
     <x:row r="71" ht="42" customHeight="1">
       <x:c r="A71" s="51" t="str">
@@ -4135,9 +3907,6 @@
       <x:c r="R71" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S71" s="51" t="str">
-        <x:v>S11</x:v>
-      </x:c>
     </x:row>
     <x:row r="72" ht="42" customHeight="1">
       <x:c r="A72" s="51" t="str">
@@ -4182,9 +3951,6 @@
       <x:c r="R72" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S72" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="73" ht="42" customHeight="1">
       <x:c r="A73" s="51" t="str">
@@ -4229,9 +3995,6 @@
       <x:c r="R73" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S73" s="51" t="str">
-        <x:v>S13;M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="74" ht="42" customHeight="1">
       <x:c r="A74" s="51" t="str">
@@ -4276,9 +4039,6 @@
       <x:c r="R74" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S74" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="75" ht="42" customHeight="1">
       <x:c r="A75" s="51" t="str">
@@ -4323,9 +4083,6 @@
       <x:c r="R75" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S75" s="51" t="str">
-        <x:v>S11</x:v>
-      </x:c>
     </x:row>
     <x:row r="76" ht="42" customHeight="1">
       <x:c r="A76" s="51" t="str">
@@ -4370,9 +4127,6 @@
       <x:c r="R76" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S76" s="51" t="str">
-        <x:v>S11</x:v>
-      </x:c>
     </x:row>
     <x:row r="77" ht="42" customHeight="1">
       <x:c r="A77" s="51" t="str">
@@ -4417,9 +4171,6 @@
       <x:c r="R77" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S77" s="51" t="str">
-        <x:v>S11</x:v>
-      </x:c>
     </x:row>
     <x:row r="78" ht="42" customHeight="1">
       <x:c r="A78" s="51" t="str">
@@ -4464,9 +4215,6 @@
       <x:c r="R78" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S78" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="79" ht="42" customHeight="1">
       <x:c r="A79" s="51" t="str">
@@ -4511,9 +4259,6 @@
       <x:c r="R79" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S79" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="80" ht="42" customHeight="1">
       <x:c r="A80" s="51" t="str">
@@ -4558,9 +4303,6 @@
       <x:c r="R80" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S80" s="51" t="str">
-        <x:v>S11</x:v>
-      </x:c>
     </x:row>
     <x:row r="81" ht="42" customHeight="1">
       <x:c r="A81" s="51" t="str">
@@ -4605,9 +4347,6 @@
       <x:c r="R81" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S81" s="51" t="str">
-        <x:v>S11</x:v>
-      </x:c>
     </x:row>
     <x:row r="82" ht="42" customHeight="1">
       <x:c r="A82" s="51" t="str">
@@ -4652,9 +4391,6 @@
       <x:c r="R82" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S82" s="51" t="str">
-        <x:v>S11</x:v>
-      </x:c>
     </x:row>
     <x:row r="83" ht="42" customHeight="1">
       <x:c r="A83" s="51" t="str">
@@ -4699,9 +4435,6 @@
       <x:c r="R83" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S83" s="51" t="str">
-        <x:v>S11</x:v>
-      </x:c>
     </x:row>
     <x:row r="84" ht="42" customHeight="1">
       <x:c r="A84" s="51" t="str">
@@ -4746,9 +4479,6 @@
       <x:c r="R84" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S84" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="85" ht="42" customHeight="1">
       <x:c r="A85" s="51" t="str">
@@ -4793,9 +4523,6 @@
       <x:c r="R85" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S85" s="51" t="str">
-        <x:v>S11</x:v>
-      </x:c>
     </x:row>
     <x:row r="86" ht="42" customHeight="1">
       <x:c r="A86" s="51" t="str">
@@ -4840,9 +4567,6 @@
       <x:c r="R86" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S86" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="87" ht="42" customHeight="1">
       <x:c r="A87" s="51" t="str">
@@ -4887,9 +4611,6 @@
       <x:c r="R87" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S87" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="88" ht="42" customHeight="1">
       <x:c r="A88" s="51" t="str">
@@ -4934,9 +4655,6 @@
       <x:c r="R88" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S88" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="89" ht="42" customHeight="1">
       <x:c r="A89" s="51" t="str">
@@ -4981,9 +4699,6 @@
       <x:c r="R89" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S89" s="51" t="str">
-        <x:v>S11</x:v>
-      </x:c>
     </x:row>
     <x:row r="90" ht="42" customHeight="1">
       <x:c r="A90" s="51" t="str">
@@ -5028,9 +4743,6 @@
       <x:c r="R90" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S90" s="51" t="str">
-        <x:v>S11</x:v>
-      </x:c>
     </x:row>
     <x:row r="91" ht="42" customHeight="1">
       <x:c r="A91" s="51" t="str">
@@ -5075,9 +4787,6 @@
       <x:c r="R91" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S91" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="92" ht="42" customHeight="1">
       <x:c r="A92" s="51" t="str">
@@ -5122,9 +4831,6 @@
       <x:c r="R92" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S92" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="93" ht="42" customHeight="1">
       <x:c r="A93" s="51" t="str">
@@ -5169,9 +4875,6 @@
       <x:c r="R93" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S93" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="94" ht="42" customHeight="1">
       <x:c r="A94" s="51" t="str">
@@ -5216,9 +4919,6 @@
       <x:c r="R94" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S94" s="51" t="str">
-        <x:v>S10;M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="95" ht="42" customHeight="1">
       <x:c r="A95" s="51" t="str">
@@ -5263,9 +4963,6 @@
       <x:c r="R95" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S95" s="51" t="str">
-        <x:v>S12</x:v>
-      </x:c>
     </x:row>
     <x:row r="96" ht="42" customHeight="1">
       <x:c r="A96" s="51" t="str">
@@ -5310,9 +5007,6 @@
       <x:c r="R96" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S96" s="51" t="str">
-        <x:v>S10;S12</x:v>
-      </x:c>
     </x:row>
     <x:row r="97" ht="42" customHeight="1">
       <x:c r="A97" s="51" t="str">
@@ -5357,9 +5051,6 @@
       <x:c r="R97" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S97" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="98" ht="42" customHeight="1">
       <x:c r="A98" s="51" t="str">
@@ -5404,9 +5095,6 @@
       <x:c r="R98" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S98" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="99" ht="42" customHeight="1">
       <x:c r="A99" s="51" t="str">
@@ -5451,9 +5139,6 @@
       <x:c r="R99" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S99" s="51" t="str">
-        <x:v>S12</x:v>
-      </x:c>
     </x:row>
     <x:row r="100" ht="42" customHeight="1">
       <x:c r="A100" s="51" t="str">
@@ -5498,9 +5183,6 @@
       <x:c r="R100" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S100" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="101" ht="42" customHeight="1">
       <x:c r="A101" s="51" t="str">
@@ -5545,9 +5227,6 @@
       <x:c r="R101" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S101" s="51" t="str">
-        <x:v>S11</x:v>
-      </x:c>
     </x:row>
     <x:row r="102" ht="42" customHeight="1">
       <x:c r="A102" s="51" t="str">
@@ -5592,9 +5271,6 @@
       <x:c r="R102" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S102" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="103" ht="42" customHeight="1">
       <x:c r="A103" s="51" t="str">
@@ -5639,9 +5315,6 @@
       <x:c r="R103" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S103" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="104" ht="42" customHeight="1">
       <x:c r="A104" s="51" t="str">
@@ -5686,9 +5359,6 @@
       <x:c r="R104" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S104" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="105" ht="42" customHeight="1">
       <x:c r="A105" s="51" t="str">
@@ -5733,9 +5403,6 @@
       <x:c r="R105" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S105" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="106" ht="42" customHeight="1">
       <x:c r="A106" s="51" t="str">
@@ -5780,9 +5447,6 @@
       <x:c r="R106" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S106" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="107" ht="42" customHeight="1">
       <x:c r="A107" s="51" t="str">
@@ -5827,9 +5491,6 @@
       <x:c r="R107" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S107" s="51" t="str">
-        <x:v>M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="108" ht="42" customHeight="1">
       <x:c r="A108" s="51" t="str">
@@ -5874,9 +5535,6 @@
       <x:c r="R108" s="51" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S108" s="51" t="str">
-        <x:v>S10;M01</x:v>
-      </x:c>
     </x:row>
     <x:row r="109" ht="42" customHeight="1">
       <x:c r="A109" s="52" t="str">
@@ -5921,14 +5579,11 @@
       <x:c r="R109" s="52" t="str">
         <x:v>Keep</x:v>
       </x:c>
-      <x:c r="S109" s="52" t="str">
-        <x:v>S13;M01</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A2:S2"/>
-    <x:mergeCell ref="A3:S3"/>
+    <x:mergeCell ref="A2:R2"/>
+    <x:mergeCell ref="A3:R3"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="J6:J109">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Complete"/>
@@ -5954,7 +5609,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R420df318ff4b4896"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb2e5ab206af4a85"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6318,7 +5973,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97a9e9ed7eb54263"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R620154812644423e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6883,7 +6538,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R186dfa1005b14155"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3f78670b6e7461d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8289,7 +7944,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4676e5bcd3e9468d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc47899729074fe4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9240,192 +8895,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69c32e49839b43ed"/>
-  </x:tableParts>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr>
-    <x:tabColor rgb="FF1A1A18"/>
-  </x:sheetPr>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="58" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="44" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="2" t="str">
-        <x:v>Integration Sources</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="18" customHeight="1">
-      <x:c r="A3" s="4" t="str">
-        <x:v>Source register — URLs and access dates are included for auditability.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="5"/>
-      <x:c r="B4" s="5"/>
-      <x:c r="C4" s="5"/>
-      <x:c r="D4" s="5"/>
-      <x:c r="E4" s="5"/>
-      <x:c r="F4" s="5"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="50" t="str">
-        <x:v>Source ID</x:v>
-      </x:c>
-      <x:c r="B5" s="50" t="str">
-        <x:v>Organization</x:v>
-      </x:c>
-      <x:c r="C5" s="50" t="str">
-        <x:v>Resource</x:v>
-      </x:c>
-      <x:c r="D5" s="50" t="str">
-        <x:v>Accessed</x:v>
-      </x:c>
-      <x:c r="E5" s="50" t="str">
-        <x:v>URL</x:v>
-      </x:c>
-      <x:c r="F5" s="50" t="str">
-        <x:v>Use in this workbook</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="42" customHeight="1">
-      <x:c r="A6" s="51" t="str">
-        <x:v>S10</x:v>
-      </x:c>
-      <x:c r="B6" s="51" t="str">
-        <x:v>Bain &amp; Company</x:v>
-      </x:c>
-      <x:c r="C6" s="51" t="str">
-        <x:v>The 10 Steps to Successful M&amp;A Integration</x:v>
-      </x:c>
-      <x:c r="D6" s="51" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-      <x:c r="E6" s="55" t="str">
-        <x:v>https://www.bain.com/insights/10-steps-to-successful-ma-integration/</x:v>
-      </x:c>
-      <x:c r="F6" s="51" t="str">
-        <x:v>Start during diligence; integration thesis follows deal thesis; follow the money</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="42" customHeight="1">
-      <x:c r="A7" s="51" t="str">
-        <x:v>S11</x:v>
-      </x:c>
-      <x:c r="B7" s="51" t="str">
-        <x:v>Deloitte</x:v>
-      </x:c>
-      <x:c r="C7" s="51" t="str">
-        <x:v>M&amp;A integration plan for Day One readiness</x:v>
-      </x:c>
-      <x:c r="D7" s="51" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-      <x:c r="E7" s="55" t="str">
-        <x:v>https://www.deloitte.com/us/en/services/consulting/articles/mergers-acquisitions-integration-plan-checklist.html</x:v>
-      </x:c>
-      <x:c r="F7" s="51" t="str">
-        <x:v>Business continuity, functional readiness and Day 1 checkpoints</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="42" customHeight="1">
-      <x:c r="A8" s="51" t="str">
-        <x:v>S12</x:v>
-      </x:c>
-      <x:c r="B8" s="51" t="str">
-        <x:v>EY</x:v>
-      </x:c>
-      <x:c r="C8" s="51" t="str">
-        <x:v>Nine steps to setting up an M&amp;A integration program</x:v>
-      </x:c>
-      <x:c r="D8" s="51" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-      <x:c r="E8" s="55" t="str">
-        <x:v>https://www.ey.com/en_uk/insights/mergers-acquisitions/nine-steps-to-setting-up-an-m-a-integration-program</x:v>
-      </x:c>
-      <x:c r="F8" s="51" t="str">
-        <x:v>IMO, workstream charters, interdependencies, simulations and synergy capture</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="42" customHeight="1">
-      <x:c r="A9" s="51" t="str">
-        <x:v>S13</x:v>
-      </x:c>
-      <x:c r="B9" s="51" t="str">
-        <x:v>McKinsey</x:v>
-      </x:c>
-      <x:c r="C9" s="51" t="str">
-        <x:v>Gen AI in M&amp;A: From theory to practice to high performance</x:v>
-      </x:c>
-      <x:c r="D9" s="51" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-      <x:c r="E9" s="55" t="str">
-        <x:v>https://www.mckinsey.com/capabilities/m-and-a/our-insights/gen-ai-in-m-and-a-from-theory-to-practice-to-high-performance</x:v>
-      </x:c>
-      <x:c r="F9" s="51" t="str">
-        <x:v>Practical AI use across diligence and integration; internal deal knowledge</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="42" customHeight="1">
-      <x:c r="A10" s="51" t="str">
-        <x:v>S05</x:v>
-      </x:c>
-      <x:c r="B10" s="51" t="str">
-        <x:v>FTC</x:v>
-      </x:c>
-      <x:c r="C10" s="51" t="str">
-        <x:v>Premerger Notification Program</x:v>
-      </x:c>
-      <x:c r="D10" s="51" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-      <x:c r="E10" s="55" t="str">
-        <x:v>https://www.ftc.gov/enforcement/premerger-notification-program</x:v>
-      </x:c>
-      <x:c r="F10" s="51" t="str">
-        <x:v>Pre-close conduct and regulatory process; confirm with counsel</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="42" customHeight="1">
-      <x:c r="A11" s="52" t="str">
-        <x:v>M01</x:v>
-      </x:c>
-      <x:c r="B11" s="52" t="str">
-        <x:v>Mike Ye</x:v>
-      </x:c>
-      <x:c r="C11" s="52" t="str">
-        <x:v>Acquisition Lens Judgment Doctrine</x:v>
-      </x:c>
-      <x:c r="D11" s="52" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-      <x:c r="E11" s="56" t="str">
-        <x:v>Internal MikeYe.com doctrine repository</x:v>
-      </x:c>
-      <x:c r="F11" s="52" t="str">
-        <x:v>Protect revenue while integrating cost; workflow disposition; evidence; standalone view when useful</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A2:F2"/>
-    <x:mergeCell ref="A3:F3"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra89f95dc67364944"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a1590722a8e4051"/>
   </x:tableParts>
 </x:worksheet>
 </file>